--- a/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-09/Resumo_Estatisticas.xlsx
+++ b/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-09/Resumo_Estatisticas.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.611165219555952</v>
+        <v>-12.77005447533083</v>
       </c>
       <c r="D2" t="n">
-        <v>3.585806637948469</v>
+        <v>6.260534354849745</v>
       </c>
       <c r="E2" t="n">
-        <v>2.24575186522681</v>
+        <v>4.523951583696813</v>
       </c>
       <c r="F2" t="n">
-        <v>3.083999390465571</v>
+        <v>2.056807717075524</v>
       </c>
     </row>
     <row r="3">
@@ -497,16 +497,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-2.452188583567738</v>
+        <v>-2.054404642598102</v>
       </c>
       <c r="D3" t="n">
-        <v>3.668849723236784</v>
+        <v>2.247238055495944</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7979232017016302</v>
+        <v>0.7059812268990953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8480012742240717</v>
+        <v>0.5194164052225466</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.792505204270775</v>
+        <v>-0.4982342528852095</v>
       </c>
       <c r="D4" t="n">
-        <v>3.440348372133253</v>
+        <v>1.752210619448613</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6556280570739464</v>
+        <v>0.3517574150832339</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8077295309708317</v>
+        <v>0.4113863215927018</v>
       </c>
     </row>
     <row r="5">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.750971134921306</v>
+        <v>-3.249051583785017</v>
       </c>
       <c r="D5" t="n">
-        <v>3.617406740398015</v>
+        <v>3.25851783870336</v>
       </c>
       <c r="E5" t="n">
-        <v>2.368068373995682</v>
+        <v>1.402302711136737</v>
       </c>
       <c r="F5" t="n">
-        <v>3.113906354404693</v>
+        <v>1.075399606100036</v>
       </c>
     </row>
     <row r="6">
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.313451875908338</v>
+        <v>-2.255990435169076</v>
       </c>
       <c r="D6" t="n">
-        <v>2.697403641013457</v>
+        <v>2.156458070488033</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3229785889481113</v>
+        <v>0.3084972258853501</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2629293119155972</v>
+        <v>0.2043191912660172</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2.022049713489858</v>
+        <v>-0.4167863712378135</v>
       </c>
       <c r="D7" t="n">
-        <v>1.096669464791883</v>
+        <v>0.6752804336685186</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3135998361308517</v>
+        <v>0.1470207362470953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1138020208315139</v>
+        <v>0.07007423881729224</v>
       </c>
     </row>
     <row r="8">
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1.333906034893955</v>
+        <v>-0.3930834644386915</v>
       </c>
       <c r="D8" t="n">
-        <v>1.424832390311885</v>
+        <v>0.4163600009249347</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1913609708986443</v>
+        <v>0.1142213098180482</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1168244588691451</v>
+        <v>0.03413807275406274</v>
       </c>
     </row>
     <row r="9">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2.338857063514429</v>
+        <v>-3.036384370383116</v>
       </c>
       <c r="D9" t="n">
-        <v>2.56717096196891</v>
+        <v>2.602747469029723</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3357255692299948</v>
+        <v>0.3682886604185218</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2581317247556983</v>
+        <v>0.2374804505264873</v>
       </c>
     </row>
     <row r="10">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.64936895733871</v>
+        <v>-3.23776162237821</v>
       </c>
       <c r="D10" t="n">
-        <v>1.103849553534108</v>
+        <v>1.466630138462289</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1611942394406123</v>
+        <v>0.3140059772702688</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1078801613472162</v>
+        <v>0.1086730852179064</v>
       </c>
     </row>
     <row r="11">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.6510694755256298</v>
+        <v>-1.366859107317481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4872295898614117</v>
+        <v>0.4129971545857117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1346341309487596</v>
+        <v>0.1930021865920561</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03973044949100534</v>
+        <v>0.03367727028825122</v>
       </c>
     </row>
     <row r="12">
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2335405219960216</v>
+        <v>-1.00662343609736</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4882091241585787</v>
+        <v>0.6386747331451031</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08069845285070612</v>
+        <v>0.2112719737887881</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05140222297178129</v>
+        <v>0.06724434144107473</v>
       </c>
     </row>
     <row r="13">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.56290431932315</v>
+        <v>-5.057525200312134</v>
       </c>
       <c r="D13" t="n">
-        <v>1.295463608198977</v>
+        <v>2.283767545618646</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1576941394764586</v>
+        <v>0.4628244066324289</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1307098690510221</v>
+        <v>0.1744909553381443</v>
       </c>
     </row>
   </sheetData>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5941483690341296</v>
+        <v>-8.078909023053395</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1716899248528229</v>
+        <v>2.902976324026822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3490556822758019</v>
+        <v>2.982743817510927</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1476631835056564</v>
+        <v>0.9537307468204458</v>
       </c>
     </row>
     <row r="3">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.28665718781524</v>
+        <v>0.6677620344244606</v>
       </c>
       <c r="D3" t="n">
-        <v>3.678079174298122</v>
+        <v>0.1657329879445568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5285275645659933</v>
+        <v>0.07679197552553653</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8501345276552038</v>
+        <v>0.03830677066651728</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5117407310884318</v>
+        <v>0.7720764219637767</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1788965597415654</v>
+        <v>0.03566770176104684</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1146341555013972</v>
+        <v>0.05351219843769406</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0420015703824639</v>
+        <v>0.008374110089436603</v>
       </c>
     </row>
     <row r="5">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7273946623809086</v>
+        <v>0.5609604529880481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1462384141926074</v>
+        <v>0.1570302594227108</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2346618873616979</v>
+        <v>0.1448950041982486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.125883750402456</v>
+        <v>0.05182426105611472</v>
       </c>
     </row>
     <row r="6">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-3.709662833106703</v>
+        <v>-3.950704349143114</v>
       </c>
       <c r="D6" t="n">
-        <v>2.299096371519486</v>
+        <v>4.153982818179099</v>
       </c>
       <c r="E6" t="n">
-        <v>0.45907419610287</v>
+        <v>0.4690672740904046</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2241043267681454</v>
+        <v>0.3935798342469995</v>
       </c>
     </row>
     <row r="7">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-3.274223854623044</v>
+        <v>0.7126645987572789</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8201183492935099</v>
+        <v>0.1528026654713185</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4435386666252015</v>
+        <v>0.02981695977471294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08510415258832651</v>
+        <v>0.01585642044148446</v>
       </c>
     </row>
     <row r="8">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.046289881914547</v>
+        <v>-1.072762376188114</v>
       </c>
       <c r="D8" t="n">
-        <v>2.30974159291155</v>
+        <v>0.9329530988482889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2497705480539499</v>
+        <v>0.1699493530670615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.189379686729598</v>
+        <v>0.07649442956542132</v>
       </c>
     </row>
     <row r="9">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-3.734901846073006</v>
+        <v>-4.076405935360488</v>
       </c>
       <c r="D9" t="n">
-        <v>2.11246674996707</v>
+        <v>1.815231431791178</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4760993319815241</v>
+        <v>0.4631825341988168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2124107407478023</v>
+        <v>0.1656257410144798</v>
       </c>
     </row>
     <row r="10">
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.2519703857600603</v>
+        <v>-6.304298082980702</v>
       </c>
       <c r="D10" t="n">
-        <v>1.383411920689828</v>
+        <v>1.547788223884625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1223561370164187</v>
+        <v>0.5412275305217742</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1352020306896556</v>
+        <v>0.1146866664896446</v>
       </c>
     </row>
     <row r="11">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1.10912250037125</v>
+        <v>-2.170706098849315</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5187825099180952</v>
+        <v>0.1491442142750835</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1719854186096908</v>
+        <v>0.2585507553984713</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04230338784017738</v>
+        <v>0.01216175453099505</v>
       </c>
     </row>
     <row r="12">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7254007289018951</v>
+        <v>-1.028502211760163</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1724108770681006</v>
+        <v>1.248678553502785</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0289118172160351</v>
+        <v>0.2135755311155939</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01815267660367661</v>
+        <v>0.1314699997421252</v>
       </c>
     </row>
     <row r="13">
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2359376689362616</v>
+        <v>-7.960087059537732</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06283776176218907</v>
+        <v>0.8908495082167412</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0770924683704587</v>
+        <v>0.6845942591360197</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006340213310055022</v>
+        <v>0.06806523809722805</v>
       </c>
     </row>
   </sheetData>
